--- a/config/business_rules_template.xlsx
+++ b/config/business_rules_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rajeevpisharody/excel_automation/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79CD85B6-FE6B-3248-AE04-9579E76D32D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2390F7-74DF-8B42-AD21-FD4F54DE1248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{E0D1B0CB-7FBB-B34F-BC6A-63C31132DB30}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" activeTab="7" xr2:uid="{E0D1B0CB-7FBB-B34F-BC6A-63C31132DB30}"/>
   </bookViews>
   <sheets>
     <sheet name="column_mapping" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="keyword_rules" sheetId="5" r:id="rId5"/>
     <sheet name="phrase_rules" sheetId="6" r:id="rId6"/>
     <sheet name="template_noise" sheetId="7" r:id="rId7"/>
+    <sheet name="final_category_consolidation" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Standard Column</t>
   </si>
@@ -108,6 +109,18 @@
   </si>
   <si>
     <t>Example template footer note</t>
+  </si>
+  <si>
+    <t>Old Category Name</t>
+  </si>
+  <si>
+    <t>Final Mapped Category</t>
+  </si>
+  <si>
+    <t>Example existing category</t>
+  </si>
+  <si>
+    <t>Example updated final category</t>
   </si>
 </sst>
 </file>
@@ -752,4 +765,34 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F9C302-109F-524A-BE51-A0ED353943F5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>